--- a/allUniversity/AllUniversity_1.xlsx
+++ b/allUniversity/AllUniversity_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\AllUniversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFFC3898-34A8-4A77-806E-6579AE5D1F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074CA607-3F84-4252-B4EE-0F0DAF889D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
   <si>
     <t>university</t>
   </si>
@@ -185,6 +184,12 @@
   </si>
   <si>
     <t>on January 15 for the summer semester.</t>
+  </si>
+  <si>
+    <t>https://www.daad.de/en/</t>
+  </si>
+  <si>
+    <t>german academic exchange sercvice</t>
   </si>
 </sst>
 </file>
@@ -345,7 +350,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -405,6 +410,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -687,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -1139,7 +1147,6 @@
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="16"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -1158,20 +1165,38 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="16">
+        <v>4991318523333</v>
+      </c>
       <c r="H16" s="9" t="s">
         <v>45</v>
       </c>
     </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B17:G17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H15" r:id="rId1" display="mailto:QUMCC@qu.edu.qa" xr:uid="{ABCED68B-E591-42A7-A247-4D87E5BB3872}"/>
+    <hyperlink ref="B17" r:id="rId2" xr:uid="{5D3F0A63-FDD7-40AC-ABB6-6A3A5DACF337}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/allUniversity/AllUniversity_1.xlsx
+++ b/allUniversity/AllUniversity_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\University2\AllUniversity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{074CA607-3F84-4252-B4EE-0F0DAF889D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02267952-8124-42EF-88AA-0185DB5DC748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,13 +183,13 @@
     <t>artificial intelligence &amp; autonomous systems</t>
   </si>
   <si>
-    <t>on January 15 for the summer semester.</t>
-  </si>
-  <si>
     <t>https://www.daad.de/en/</t>
   </si>
   <si>
     <t>german academic exchange sercvice</t>
+  </si>
+  <si>
+    <t>July, 15th</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1115,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>21</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
